--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,420 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129976940</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>685014</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6561677</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två gamla tickor på död tall.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129976914</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90648</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>889</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>685031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6561690</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129976936</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90648</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>889</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>685013</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6561705</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129976928</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>685018</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6561713</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,7 +910,7 @@
         <v>129976940</v>
       </c>
       <c r="B4" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90648</v>
+        <v>90651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90648</v>
+        <v>90651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129976928</v>
       </c>
       <c r="B7" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,6 +1319,327 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130009195</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92255</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>685160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6561999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130009940</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>685147</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6561847</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetad tallraka.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130009151</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>685139</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6562022</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129976940</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90651</v>
+        <v>90652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90651</v>
+        <v>90652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129976928</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130009195</v>
       </c>
       <c r="B8" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130009940</v>
+        <v>130009151</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,35 +1438,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685147</v>
+        <v>685139</v>
       </c>
       <c r="R9" t="n">
-        <v>6561847</v>
+        <v>6562022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,17 +1503,13 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetad tallraka.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009151</v>
+        <v>130009940</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,26 +1539,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685139</v>
+        <v>685147</v>
       </c>
       <c r="R10" t="n">
-        <v>6562022</v>
+        <v>6561847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,13 +1613,17 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetad tallraka.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129976940</v>
       </c>
       <c r="B4" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
+        <v>90669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90652</v>
+        <v>90669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129976928</v>
       </c>
       <c r="B7" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130009195</v>
       </c>
       <c r="B8" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130009151</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129976940</v>
       </c>
       <c r="B4" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90685</v>
+        <v>90687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>90687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129976928</v>
       </c>
       <c r="B7" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130009195</v>
       </c>
       <c r="B8" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130009151</v>
       </c>
       <c r="B10" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>130155094</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>90687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>130155175</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>130155377</v>
       </c>
       <c r="B16" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>130155100</v>
       </c>
       <c r="B17" t="n">
-        <v>90685</v>
+        <v>90687</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>130155389</v>
       </c>
       <c r="B18" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,7 +910,7 @@
         <v>129976940</v>
       </c>
       <c r="B4" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90687</v>
+        <v>90774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90687</v>
+        <v>90774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129976928</v>
       </c>
       <c r="B7" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130009195</v>
       </c>
       <c r="B8" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130009940</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130009151</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130121570</v>
       </c>
       <c r="B11" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>130155094</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>90774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>130155175</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>130155377</v>
       </c>
       <c r="B16" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,32 +2282,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130155100</v>
+        <v>130155389</v>
       </c>
       <c r="B17" t="n">
-        <v>90687</v>
+        <v>92160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>889</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685117</v>
+        <v>684987</v>
       </c>
       <c r="R17" t="n">
-        <v>6561718</v>
+        <v>6561666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,6 +2358,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tidigare rapporterad 2021.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2380,112 +2385,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>130155389</v>
-      </c>
-      <c r="B18" t="n">
-        <v>92073</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Phaeolus schweinitzii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Högstaskogen, Srm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>684987</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6561666</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Österhaninge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,37 +1861,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130155094</v>
+        <v>130155175</v>
       </c>
       <c r="B13" t="n">
-        <v>90774</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>889</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1899,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685152</v>
+        <v>685025</v>
       </c>
       <c r="R13" t="n">
-        <v>6561703</v>
+        <v>6561654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,6 +1936,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,38 +1968,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130155175</v>
+        <v>130155159</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2001,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685025</v>
+        <v>685023</v>
       </c>
       <c r="R14" t="n">
-        <v>6561654</v>
+        <v>6561678</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,11 +2048,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,43 +2075,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130155159</v>
+        <v>130155377</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>91749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685023</v>
+        <v>685086</v>
       </c>
       <c r="R15" t="n">
-        <v>6561678</v>
+        <v>6561624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,6 +2149,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På en gren, tallen intill betesmark.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,32 +2181,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130155377</v>
+        <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>91749</v>
+        <v>92160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685086</v>
+        <v>684987</v>
       </c>
       <c r="R16" t="n">
-        <v>6561624</v>
+        <v>6561666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,32 +2287,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130155389</v>
+        <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>92160</v>
+        <v>90774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>889</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684987</v>
+        <v>685152</v>
       </c>
       <c r="R17" t="n">
-        <v>6561666</v>
+        <v>6561703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,11 +2363,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2385,6 +2385,107 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130306117</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90774</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>889</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>685116</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6561716</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2487,120 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130328335</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6561653</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130009940</v>
+        <v>130009151</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,35 +1438,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685147</v>
+        <v>685139</v>
       </c>
       <c r="R9" t="n">
-        <v>6561847</v>
+        <v>6562022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,17 +1503,13 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetad tallraka.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009151</v>
+        <v>130009940</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,26 +1539,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685139</v>
+        <v>685147</v>
       </c>
       <c r="R10" t="n">
-        <v>6562022</v>
+        <v>6561847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,13 +1613,17 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetad tallraka.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2601,6 +2601,107 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130328836</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>685072</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6561690</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>130155175</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130155377</v>
       </c>
       <c r="B15" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>92160</v>
+        <v>92163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90774</v>
+        <v>90777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90774</v>
+        <v>90777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1645,7 +1645,7 @@
         <v>130121570</v>
       </c>
       <c r="B11" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>130155175</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130155377</v>
       </c>
       <c r="B15" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>92163</v>
+        <v>92189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90777</v>
+        <v>90803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90777</v>
+        <v>90803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>130328335</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130328836</v>
       </c>
       <c r="B20" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>130155175</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130155377</v>
       </c>
       <c r="B15" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90803</v>
+        <v>90804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90803</v>
+        <v>90804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>130155175</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130155377</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>92190</v>
+        <v>92191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90804</v>
+        <v>90805</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90804</v>
+        <v>90805</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90805</v>
+        <v>90807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90805</v>
+        <v>90807</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>130328335</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130328836</v>
       </c>
       <c r="B20" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>130328335</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130328836</v>
       </c>
       <c r="B20" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90819</v>
+        <v>90820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90819</v>
+        <v>90820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>130328335</v>
       </c>
       <c r="B19" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130328836</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -2290,7 +2290,7 @@
         <v>130155094</v>
       </c>
       <c r="B17" t="n">
-        <v>90820</v>
+        <v>90821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130306117</v>
       </c>
       <c r="B18" t="n">
-        <v>90820</v>
+        <v>90821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>130328335</v>
       </c>
       <c r="B19" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130328836</v>
       </c>
       <c r="B20" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96806135</v>
+        <v>100751968</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684987.453849873</v>
+        <v>685248</v>
       </c>
       <c r="R2" t="n">
-        <v>6561670.448804242</v>
+        <v>6561919</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +785,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99759702</v>
+        <v>100752016</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685013.1880393601</v>
+        <v>685257</v>
       </c>
       <c r="R3" t="n">
-        <v>6561712.794222295</v>
+        <v>6561879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129976940</v>
+        <v>129976843</v>
       </c>
       <c r="B4" t="n">
-        <v>91749</v>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685014</v>
+        <v>685222</v>
       </c>
       <c r="R4" t="n">
-        <v>6561677</v>
+        <v>6561733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,11 +969,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +999,7 @@
         <v>129976914</v>
       </c>
       <c r="B5" t="n">
-        <v>90774</v>
+        <v>90946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1100,7 @@
         <v>129976936</v>
       </c>
       <c r="B6" t="n">
-        <v>90774</v>
+        <v>90946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129976928</v>
+        <v>130155094</v>
       </c>
       <c r="B7" t="n">
-        <v>91749</v>
+        <v>90946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685018</v>
+        <v>685152</v>
       </c>
       <c r="R7" t="n">
-        <v>6561713</v>
+        <v>6561703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,24 +1266,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1321,32 +1299,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130009195</v>
+        <v>130306117</v>
       </c>
       <c r="B8" t="n">
-        <v>92378</v>
+        <v>90946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>889</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685160</v>
+        <v>685116</v>
       </c>
       <c r="R8" t="n">
-        <v>6561999</v>
+        <v>6561716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,24 +1367,19 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran, på halvhög stubbe samt på lågan.</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1427,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130009151</v>
+        <v>130121568</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>92134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,21 +1411,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,17 +1434,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685139</v>
+        <v>685143</v>
       </c>
       <c r="R9" t="n">
-        <v>6562022</v>
+        <v>6561740</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,43 +1468,63 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kanske 3 fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009940</v>
+        <v>130009151</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,35 +1532,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1575,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685147</v>
+        <v>685139</v>
       </c>
       <c r="R10" t="n">
-        <v>6561847</v>
+        <v>6562022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,17 +1597,13 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetad tallraka.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1642,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121570</v>
+        <v>130009195</v>
       </c>
       <c r="B11" t="n">
-        <v>44106</v>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,46 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685100</v>
+        <v>685160</v>
       </c>
       <c r="R11" t="n">
-        <v>6561680</v>
+        <v>6561999</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,17 +1690,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gräs gick in typ 10 cm</t>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,22 +1716,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121571</v>
+        <v>96806135</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,46 +1739,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685103</v>
+        <v>684987</v>
       </c>
       <c r="R12" t="n">
-        <v>6561668</v>
+        <v>6561670</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,12 +1796,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,50 +1817,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130155175</v>
+        <v>130155389</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>92348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1900,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685025</v>
+        <v>684987</v>
       </c>
       <c r="R13" t="n">
-        <v>6561654</v>
+        <v>6561666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1907,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,43 +1935,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130155159</v>
+        <v>99759702</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685023</v>
+        <v>685013</v>
       </c>
       <c r="R14" t="n">
-        <v>6561678</v>
+        <v>6561713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,12 +2003,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130155377</v>
+        <v>129976928</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685086</v>
+        <v>685018</v>
       </c>
       <c r="R15" t="n">
-        <v>6561624</v>
+        <v>6561713</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,17 +2104,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,32 +2142,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130155389</v>
+        <v>129976940</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684987</v>
+        <v>685014</v>
       </c>
       <c r="R16" t="n">
-        <v>6561666</v>
+        <v>6561677</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,17 +2210,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tidigare rapporterad 2021.</t>
+          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130155094</v>
+        <v>130125932</v>
       </c>
       <c r="B17" t="n">
-        <v>90821</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,37 +2259,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685152</v>
+        <v>685171</v>
       </c>
       <c r="R17" t="n">
-        <v>6561703</v>
+        <v>6561736</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,19 +2320,19 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
@@ -2376,22 +2341,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130306117</v>
+        <v>130155377</v>
       </c>
       <c r="B18" t="n">
-        <v>90821</v>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,21 +2364,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685116</v>
+        <v>685086</v>
       </c>
       <c r="R18" t="n">
-        <v>6561716</v>
+        <v>6561624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,11 +2429,16 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en gren, tallen intill betesmark.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
@@ -2489,14 +2459,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130328335</v>
+        <v>130009940</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2536,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685025</v>
+        <v>685147</v>
       </c>
       <c r="R19" t="n">
-        <v>6561653</v>
+        <v>6561847</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,17 +2536,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,38 +2573,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130328836</v>
+        <v>130328335</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2642,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685072</v>
+        <v>685025</v>
       </c>
       <c r="R20" t="n">
-        <v>6561690</v>
+        <v>6561653</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,12 +2650,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,6 +2684,859 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111153798</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>685167</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6561941</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130121570</v>
+      </c>
+      <c r="B22" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 59567-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>685100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6561680</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gräs gick in typ 10 cm</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129976909</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>685130</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6561726</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130328836</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>685072</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6561690</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130121567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 59567-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>685133</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6561742</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130155159</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>685023</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6561678</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130121571</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 59567-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>685103</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6561668</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130155175</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,37 +895,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129976843</v>
+        <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>92699</v>
+        <v>96629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685222</v>
+        <v>685032</v>
       </c>
       <c r="R4" t="n">
-        <v>6561733</v>
+        <v>6561763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129976914</v>
+        <v>129976843</v>
       </c>
       <c r="B5" t="n">
-        <v>90946</v>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>889</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685031</v>
+        <v>685222</v>
       </c>
       <c r="R5" t="n">
-        <v>6561690</v>
+        <v>6561733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976936</v>
+        <v>129976914</v>
       </c>
       <c r="B6" t="n">
         <v>90946</v>
@@ -1135,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685013</v>
+        <v>685031</v>
       </c>
       <c r="R6" t="n">
-        <v>6561705</v>
+        <v>6561690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155094</v>
+        <v>129976936</v>
       </c>
       <c r="B7" t="n">
         <v>90946</v>
@@ -1236,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685152</v>
+        <v>685013</v>
       </c>
       <c r="R7" t="n">
-        <v>6561703</v>
+        <v>6561705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,19 +1275,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1299,7 +1308,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130306117</v>
+        <v>130155094</v>
       </c>
       <c r="B8" t="n">
         <v>90946</v>
@@ -1337,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685116</v>
+        <v>685152</v>
       </c>
       <c r="R8" t="n">
-        <v>6561716</v>
+        <v>6561703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121568</v>
+        <v>130306117</v>
       </c>
       <c r="B9" t="n">
-        <v>92134</v>
+        <v>90946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>889</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,17 +1443,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685143</v>
+        <v>685116</v>
       </c>
       <c r="R9" t="n">
-        <v>6561740</v>
+        <v>6561716</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,17 +1477,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kanske 3 fruktkroppar på granlåga</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,40 +1495,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009151</v>
+        <v>130121568</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,17 +1544,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685139</v>
+        <v>685143</v>
       </c>
       <c r="R10" t="n">
-        <v>6562022</v>
+        <v>6561740</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,65 +1578,85 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kanske 3 fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130009195</v>
+        <v>130009151</v>
       </c>
       <c r="B11" t="n">
-        <v>92564</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685160</v>
+        <v>685139</v>
       </c>
       <c r="R11" t="n">
-        <v>6561999</v>
+        <v>6562022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96806135</v>
+        <v>130009195</v>
       </c>
       <c r="B12" t="n">
-        <v>92348</v>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,13 +1770,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684987</v>
+        <v>685160</v>
       </c>
       <c r="R12" t="n">
-        <v>6561670</v>
+        <v>6561999</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,12 +1800,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130155389</v>
+        <v>96806135</v>
       </c>
       <c r="B13" t="n">
         <v>92348</v>
@@ -1870,10 +1879,10 @@
         <v>684987</v>
       </c>
       <c r="R13" t="n">
-        <v>6561666</v>
+        <v>6561670</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,17 +1906,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,32 +1939,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99759702</v>
+        <v>130155389</v>
       </c>
       <c r="B14" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685013</v>
+        <v>684987</v>
       </c>
       <c r="R14" t="n">
-        <v>6561713</v>
+        <v>6561666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,12 +2007,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2045,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129976928</v>
+        <v>99759702</v>
       </c>
       <c r="B15" t="n">
         <v>91930</v>
@@ -2074,7 +2083,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685018</v>
+        <v>685013</v>
       </c>
       <c r="R15" t="n">
         <v>6561713</v>
@@ -2104,17 +2113,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,7 +2146,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129976940</v>
+        <v>129976928</v>
       </c>
       <c r="B16" t="n">
         <v>91930</v>
@@ -2180,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685014</v>
+        <v>685018</v>
       </c>
       <c r="R16" t="n">
-        <v>6561677</v>
+        <v>6561713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två gamla tickor på död tall.</t>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,7 +2252,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130125932</v>
+        <v>129976940</v>
       </c>
       <c r="B17" t="n">
         <v>91930</v>
@@ -2276,24 +2280,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685171</v>
+        <v>685014</v>
       </c>
       <c r="R17" t="n">
-        <v>6561736</v>
+        <v>6561677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,12 +2320,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,19 +2346,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130155377</v>
+        <v>130125932</v>
       </c>
       <c r="B18" t="n">
         <v>91930</v>
@@ -2381,20 +2386,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685086</v>
+        <v>685171</v>
       </c>
       <c r="R18" t="n">
-        <v>6561624</v>
+        <v>6561736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,17 +2430,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2447,58 +2451,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130009940</v>
+        <v>130155377</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2506,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685147</v>
+        <v>685086</v>
       </c>
       <c r="R19" t="n">
-        <v>6561847</v>
+        <v>6561624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,17 +2531,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bearbetad tallraka.</t>
+          <t>På en gren, tallen intill betesmark.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,6 +2550,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2573,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130328335</v>
+        <v>130009940</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2620,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685025</v>
+        <v>685147</v>
       </c>
       <c r="R20" t="n">
-        <v>6561653</v>
+        <v>6561847</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,17 +2646,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111153798</v>
+        <v>130328335</v>
       </c>
       <c r="B21" t="n">
-        <v>56895</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,16 +2694,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2720,21 +2716,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685167</v>
+        <v>685025</v>
       </c>
       <c r="R21" t="n">
-        <v>6561941</v>
+        <v>6561653</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,12 +2760,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,7 +2779,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2794,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130121570</v>
+        <v>111153798</v>
       </c>
       <c r="B22" t="n">
-        <v>44177</v>
+        <v>56895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,46 +2808,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101735</v>
+        <v>100088</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685100</v>
+        <v>685167</v>
       </c>
       <c r="R22" t="n">
-        <v>6561680</v>
+        <v>6561941</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2868,17 +2871,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gräs gick in typ 10 cm</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,68 +2892,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129976909</v>
+        <v>130121570</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>44177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685130</v>
+        <v>685100</v>
       </c>
       <c r="R23" t="n">
-        <v>6561726</v>
+        <v>6561680</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2979,12 +2978,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gräs gick in typ 10 cm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,25 +2997,26 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130328836</v>
+        <v>129976909</v>
       </c>
       <c r="B24" t="n">
         <v>58114</v>
@@ -3042,7 +3047,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3050,13 +3059,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685072</v>
+        <v>685130</v>
       </c>
       <c r="R24" t="n">
-        <v>6561690</v>
+        <v>6561726</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,12 +3089,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3112,57 +3121,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130121567</v>
+        <v>130328836</v>
       </c>
       <c r="B25" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685133</v>
+        <v>685072</v>
       </c>
       <c r="R25" t="n">
-        <v>6561742</v>
+        <v>6561690</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3186,12 +3190,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,29 +3204,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130155159</v>
+        <v>130121567</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,21 +3233,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,17 +3262,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685023</v>
+        <v>685133</v>
       </c>
       <c r="R26" t="n">
-        <v>6561678</v>
+        <v>6561742</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3293,12 +3296,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3314,22 +3317,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130121571</v>
+        <v>130155159</v>
       </c>
       <c r="B27" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,21 +3340,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3366,17 +3369,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685103</v>
+        <v>685023</v>
       </c>
       <c r="R27" t="n">
-        <v>6561668</v>
+        <v>6561678</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3400,12 +3403,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3421,64 +3424,69 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130155175</v>
+        <v>130121571</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>8444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685025</v>
+        <v>685103</v>
       </c>
       <c r="R28" t="n">
-        <v>6561654</v>
+        <v>6561668</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3502,17 +3510,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,15 +3531,122 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130155175</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100751968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100752016</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135450711</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976914</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976936</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155094</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130306117</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009151</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1835,6 +1890,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96806135</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155389</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99759702</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976928</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2355,6 +2435,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976940</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2460,6 +2545,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130125932</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155377</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009940</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130328335</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2901,6 +3006,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111153798</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3013,6 +3123,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121570</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3118,6 +3233,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976909</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130328836</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3326,6 +3451,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121567</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3433,6 +3563,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155159</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121571</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3647,8 +3787,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155175</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>96629</v>
+        <v>96673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>96673</v>
+        <v>96700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,37 +910,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129976843</v>
+        <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>92699</v>
+        <v>96705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685222</v>
+        <v>685032</v>
       </c>
       <c r="R4" t="n">
-        <v>6561733</v>
+        <v>6561763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +1019,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976843</t>
+          <t>https://artportalen.se/Sighting/135450711</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129976914</v>
+        <v>129976843</v>
       </c>
       <c r="B5" t="n">
-        <v>90946</v>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>889</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685031</v>
+        <v>685222</v>
       </c>
       <c r="R5" t="n">
-        <v>6561690</v>
+        <v>6561733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,13 +1125,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976914</t>
+          <t>https://artportalen.se/Sighting/129976843</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976936</v>
+        <v>129976914</v>
       </c>
       <c r="B6" t="n">
         <v>90946</v>
@@ -1160,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685013</v>
+        <v>685031</v>
       </c>
       <c r="R6" t="n">
-        <v>6561705</v>
+        <v>6561690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,13 +1231,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976936</t>
+          <t>https://artportalen.se/Sighting/129976914</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155094</v>
+        <v>129976936</v>
       </c>
       <c r="B7" t="n">
         <v>90946</v>
@@ -1266,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685152</v>
+        <v>685013</v>
       </c>
       <c r="R7" t="n">
-        <v>6561703</v>
+        <v>6561705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,19 +1305,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1328,13 +1337,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155094</t>
+          <t>https://artportalen.se/Sighting/129976936</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130306117</v>
+        <v>130155094</v>
       </c>
       <c r="B8" t="n">
         <v>90946</v>
@@ -1372,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685116</v>
+        <v>685152</v>
       </c>
       <c r="R8" t="n">
-        <v>6561716</v>
+        <v>6561703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,16 +1443,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130306117</t>
+          <t>https://artportalen.se/Sighting/130155094</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121568</v>
+        <v>130306117</v>
       </c>
       <c r="B9" t="n">
-        <v>92134</v>
+        <v>90946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>889</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,17 +1483,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685143</v>
+        <v>685116</v>
       </c>
       <c r="R9" t="n">
-        <v>6561740</v>
+        <v>6561716</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,17 +1517,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kanske 3 fruktkroppar på granlåga</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,45 +1535,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121568</t>
+          <t>https://artportalen.se/Sighting/130306117</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009151</v>
+        <v>130121568</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,17 +1589,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685139</v>
+        <v>685143</v>
       </c>
       <c r="R10" t="n">
-        <v>6562022</v>
+        <v>6561740</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,70 +1623,90 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kanske 3 fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009151</t>
+          <t>https://artportalen.se/Sighting/130121568</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130009195</v>
+        <v>130009151</v>
       </c>
       <c r="B11" t="n">
-        <v>92564</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685160</v>
+        <v>685139</v>
       </c>
       <c r="R11" t="n">
-        <v>6561999</v>
+        <v>6562022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,11 +1757,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran, på halvhög stubbe samt på lågan.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1777,16 +1781,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009195</t>
+          <t>https://artportalen.se/Sighting/130009151</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96806135</v>
+        <v>130009195</v>
       </c>
       <c r="B12" t="n">
-        <v>92348</v>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,21 +1798,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684987</v>
+        <v>685160</v>
       </c>
       <c r="R12" t="n">
-        <v>6561670</v>
+        <v>6561999</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,12 +1855,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,13 +1892,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96806135</t>
+          <t>https://artportalen.se/Sighting/130009195</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130155389</v>
+        <v>96806135</v>
       </c>
       <c r="B13" t="n">
         <v>92348</v>
@@ -1930,10 +1939,10 @@
         <v>684987</v>
       </c>
       <c r="R13" t="n">
-        <v>6561666</v>
+        <v>6561670</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1957,17 +1966,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,38 +1998,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155389</t>
+          <t>https://artportalen.se/Sighting/96806135</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99759702</v>
+        <v>130155389</v>
       </c>
       <c r="B14" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685013</v>
+        <v>684987</v>
       </c>
       <c r="R14" t="n">
-        <v>6561713</v>
+        <v>6561666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,12 +2072,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,13 +2109,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99759702</t>
+          <t>https://artportalen.se/Sighting/130155389</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129976928</v>
+        <v>99759702</v>
       </c>
       <c r="B15" t="n">
         <v>91930</v>
@@ -2144,7 +2153,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685018</v>
+        <v>685013</v>
       </c>
       <c r="R15" t="n">
         <v>6561713</v>
@@ -2174,17 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,13 +2215,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976928</t>
+          <t>https://artportalen.se/Sighting/99759702</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129976940</v>
+        <v>129976928</v>
       </c>
       <c r="B16" t="n">
         <v>91930</v>
@@ -2255,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685014</v>
+        <v>685018</v>
       </c>
       <c r="R16" t="n">
-        <v>6561677</v>
+        <v>6561713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2299,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två gamla tickor på död tall.</t>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,13 +2326,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976940</t>
+          <t>https://artportalen.se/Sighting/129976928</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130125932</v>
+        <v>129976940</v>
       </c>
       <c r="B17" t="n">
         <v>91930</v>
@@ -2356,24 +2360,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685171</v>
+        <v>685014</v>
       </c>
       <c r="R17" t="n">
-        <v>6561736</v>
+        <v>6561677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,12 +2400,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,24 +2426,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130125932</t>
+          <t>https://artportalen.se/Sighting/129976940</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130155377</v>
+        <v>130125932</v>
       </c>
       <c r="B18" t="n">
         <v>91930</v>
@@ -2466,20 +2471,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685086</v>
+        <v>685171</v>
       </c>
       <c r="R18" t="n">
-        <v>6561624</v>
+        <v>6561736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,17 +2515,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,63 +2536,54 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155377</t>
+          <t>https://artportalen.se/Sighting/130125932</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130009940</v>
+        <v>130155377</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685147</v>
+        <v>685086</v>
       </c>
       <c r="R19" t="n">
-        <v>6561847</v>
+        <v>6561624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,17 +2621,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bearbetad tallraka.</t>
+          <t>På en gren, tallen intill betesmark.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,6 +2640,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2662,13 +2658,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009940</t>
+          <t>https://artportalen.se/Sighting/130155377</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130328335</v>
+        <v>130009940</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2715,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685025</v>
+        <v>685147</v>
       </c>
       <c r="R20" t="n">
-        <v>6561653</v>
+        <v>6561847</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,17 +2741,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,16 +2777,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328335</t>
+          <t>https://artportalen.se/Sighting/130009940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111153798</v>
+        <v>130328335</v>
       </c>
       <c r="B21" t="n">
-        <v>56895</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,16 +2794,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2820,21 +2816,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685167</v>
+        <v>685025</v>
       </c>
       <c r="R21" t="n">
-        <v>6561941</v>
+        <v>6561653</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,12 +2860,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,7 +2879,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2893,16 +2896,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111153798</t>
+          <t>https://artportalen.se/Sighting/130328335</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130121570</v>
+        <v>111153798</v>
       </c>
       <c r="B22" t="n">
-        <v>44177</v>
+        <v>56895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,46 +2913,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101735</v>
+        <v>100088</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685100</v>
+        <v>685167</v>
       </c>
       <c r="R22" t="n">
-        <v>6561680</v>
+        <v>6561941</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,17 +2976,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gräs gick in typ 10 cm</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,73 +2997,74 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121570</t>
+          <t>https://artportalen.se/Sighting/111153798</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129976909</v>
+        <v>130121570</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>44177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685130</v>
+        <v>685100</v>
       </c>
       <c r="R23" t="n">
-        <v>6561726</v>
+        <v>6561680</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3089,12 +3088,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gräs gick in typ 10 cm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,30 +3107,31 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976909</t>
+          <t>https://artportalen.se/Sighting/130121570</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130328836</v>
+        <v>129976909</v>
       </c>
       <c r="B24" t="n">
         <v>58114</v>
@@ -3157,7 +3162,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3165,13 +3174,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685072</v>
+        <v>685130</v>
       </c>
       <c r="R24" t="n">
-        <v>6561690</v>
+        <v>6561726</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,12 +3204,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,63 +3235,58 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328836</t>
+          <t>https://artportalen.se/Sighting/129976909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130121567</v>
+        <v>130328836</v>
       </c>
       <c r="B25" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685133</v>
+        <v>685072</v>
       </c>
       <c r="R25" t="n">
-        <v>6561742</v>
+        <v>6561690</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,12 +3310,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,34 +3324,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121567</t>
+          <t>https://artportalen.se/Sighting/130328836</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130155159</v>
+        <v>130121567</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,21 +3358,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3384,17 +3387,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685023</v>
+        <v>685133</v>
       </c>
       <c r="R26" t="n">
-        <v>6561678</v>
+        <v>6561742</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,12 +3421,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,27 +3442,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155159</t>
+          <t>https://artportalen.se/Sighting/130121567</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130121571</v>
+        <v>130155159</v>
       </c>
       <c r="B27" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,21 +3470,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3496,17 +3499,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685103</v>
+        <v>685023</v>
       </c>
       <c r="R27" t="n">
-        <v>6561668</v>
+        <v>6561678</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,12 +3533,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,69 +3554,74 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121571</t>
+          <t>https://artportalen.se/Sighting/130155159</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130155175</v>
+        <v>130121571</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>8444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685025</v>
+        <v>685103</v>
       </c>
       <c r="R28" t="n">
-        <v>6561654</v>
+        <v>6561668</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3637,17 +3645,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,16 +3666,128 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121571</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130155175</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130155175</t>
         </is>
@@ -3707,6 +3822,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>135450711</v>
       </c>
       <c r="B4" t="n">
-        <v>96707</v>
+        <v>96724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
